--- a/data/Hermenches/investment_decision/Hermenches_district_investment_decision.xlsx
+++ b/data/Hermenches/investment_decision/Hermenches_district_investment_decision.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,52 +440,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -505,25 +505,25 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3.470919934350114</v>
+        <v>1.002774612488435</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1.057189028300619</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.057189028300619</v>
+        <v>1.002774612488435</v>
       </c>
     </row>
     <row r="3">
@@ -542,25 +542,25 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3.470919934350114</v>
+        <v>1.488379470582734</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1.569144677828686</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.569144677828686</v>
+        <v>1.488379470582734</v>
       </c>
     </row>
     <row r="4">
@@ -579,25 +579,25 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>3.470919934350114</v>
+        <v>1.770880262100316</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.866975051233829</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.866975051233829</v>
+        <v>1.770880262100316</v>
       </c>
     </row>
     <row r="5">
@@ -616,25 +616,25 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>3.470919934350114</v>
+        <v>1.954403657032222</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2.060457132991987</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.060457132991987</v>
+        <v>1.954403657032222</v>
       </c>
     </row>
     <row r="6">
@@ -653,25 +653,25 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3.470919934350114</v>
+        <v>2.082856964215745</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.195880811764982</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2.195880811764982</v>
+        <v>2.082856964215745</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.08077124940774524</v>
+        <v>0.08107694156772063</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -690,25 +690,25 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3.470919934350114</v>
+        <v>1.002774612488435</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08061497593976577</v>
+        <v>0.08107694156772062</v>
       </c>
       <c r="G7" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H7" t="n">
-        <v>0.080893446900325</v>
+        <v>0.08107694156772063</v>
       </c>
       <c r="I7" t="n">
-        <v>1.057189028300619</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08083243931633535</v>
+        <v>0.08107694156772061</v>
       </c>
       <c r="K7" t="n">
-        <v>1.057189028300619</v>
+        <v>1.002774612488435</v>
       </c>
     </row>
     <row r="8">
@@ -716,7 +716,7 @@
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>0.08077124940774524</v>
+        <v>0.08176476766181393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -727,25 +727,25 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3.470919934350114</v>
+        <v>1.488379470582734</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08061497593976577</v>
+        <v>0.08166422014075095</v>
       </c>
       <c r="G8" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08089344690032503</v>
+        <v>0.08166422014075093</v>
       </c>
       <c r="I8" t="n">
-        <v>1.569144677828686</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08083243931633535</v>
+        <v>0.08176476766181393</v>
       </c>
       <c r="K8" t="n">
-        <v>1.569144677828686</v>
+        <v>1.488379470582734</v>
       </c>
     </row>
     <row r="9">
@@ -753,7 +753,7 @@
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>0.08163600918417009</v>
+        <v>0.08262513138655603</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -764,25 +764,25 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>3.470919934350114</v>
+        <v>1.770880262100316</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08163600918417009</v>
+        <v>0.08261203023901018</v>
       </c>
       <c r="G9" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08167245557960899</v>
+        <v>0.08261203023901016</v>
       </c>
       <c r="I9" t="n">
-        <v>1.866975051233829</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08171430164745737</v>
+        <v>0.08260826706804172</v>
       </c>
       <c r="K9" t="n">
-        <v>1.866975051233829</v>
+        <v>1.770880262100316</v>
       </c>
     </row>
     <row r="10">
@@ -790,7 +790,7 @@
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>0.08175126649824413</v>
+        <v>0.08262513138655601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3.470919934350114</v>
+        <v>1.954403657032222</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08175126649824412</v>
+        <v>0.08133311667316744</v>
       </c>
       <c r="G10" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08175126649824412</v>
+        <v>0.08106090679216499</v>
       </c>
       <c r="I10" t="n">
-        <v>2.060457132991987</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08175126649824413</v>
+        <v>0.08261203023901018</v>
       </c>
       <c r="K10" t="n">
-        <v>2.060457132991987</v>
+        <v>1.954403657032222</v>
       </c>
     </row>
     <row r="11">
@@ -827,7 +827,7 @@
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>0.08175126649824413</v>
+        <v>0.08193730529246272</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -838,25 +838,25 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3.470919934350114</v>
+        <v>2.082856964215745</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08175126649824412</v>
+        <v>0.08102196079476225</v>
       </c>
       <c r="G11" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0817512664982441</v>
+        <v>0.08076210030521676</v>
       </c>
       <c r="I11" t="n">
-        <v>2.195880811764982</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08175126649824413</v>
+        <v>0.08192420414491686</v>
       </c>
       <c r="K11" t="n">
-        <v>2.195880811764982</v>
+        <v>2.082856964215745</v>
       </c>
     </row>
     <row r="12">
@@ -875,7 +875,7 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.0361830095566004</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0361830095566004</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.06235215139065679</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06235215139065679</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.08284414207442109</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08284414207442109</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.09971239592410397</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09971239592410397</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.1140828146841643</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1140828146841643</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00339846925373222</v>
+        <v>0.003412443752473951</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1060,25 +1060,25 @@
         <v>175</v>
       </c>
       <c r="E17" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="F17" t="n">
-        <v>0.003391325323767447</v>
+        <v>0.003412443752473951</v>
       </c>
       <c r="G17" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00340405542482158</v>
+        <v>0.003412443752473951</v>
       </c>
       <c r="I17" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="J17" t="n">
-        <v>0.003401266506696339</v>
+        <v>0.003412443752473951</v>
       </c>
       <c r="K17" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
     </row>
     <row r="18">
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00339846925373222</v>
+        <v>0.003443887231061067</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1097,25 +1097,25 @@
         <v>175</v>
       </c>
       <c r="E18" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="F18" t="n">
-        <v>0.003391325323767447</v>
+        <v>0.003439290772955338</v>
       </c>
       <c r="G18" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00340405542482158</v>
+        <v>0.003439290772955337</v>
       </c>
       <c r="I18" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="J18" t="n">
-        <v>0.003401266506696339</v>
+        <v>0.003443887231061074</v>
       </c>
       <c r="K18" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
     </row>
     <row r="19">
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.003438001129225927</v>
+        <v>0.003510231617690212</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
         <v>175</v>
       </c>
       <c r="E19" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003438001129225927</v>
+        <v>0.003497220638844078</v>
       </c>
       <c r="G19" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="H19" t="n">
-        <v>0.003439667250160277</v>
+        <v>0.003497220638844079</v>
       </c>
       <c r="I19" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="J19" t="n">
-        <v>0.003441580213261916</v>
+        <v>0.003493483367914731</v>
       </c>
       <c r="K19" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
     </row>
     <row r="20">
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.003881676400752538</v>
+        <v>0.003941639315975926</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1171,25 +1171,25 @@
         <v>175</v>
       </c>
       <c r="E20" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="F20" t="n">
-        <v>0.003881676400752538</v>
+        <v>0.003904701122929663</v>
       </c>
       <c r="G20" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="H20" t="n">
-        <v>0.003933724470534174</v>
+        <v>0.00391714500320406</v>
       </c>
       <c r="I20" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="J20" t="n">
-        <v>0.003927258003375558</v>
+        <v>0.003846236502776852</v>
       </c>
       <c r="K20" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
     </row>
     <row r="21">
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.003881676400752538</v>
+        <v>0.003973082794563049</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1208,25 +1208,25 @@
         <v>175</v>
       </c>
       <c r="E21" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003881676400752538</v>
+        <v>0.003918925391656758</v>
       </c>
       <c r="G21" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="H21" t="n">
-        <v>0.003933724470534175</v>
+        <v>0.003930804728321693</v>
       </c>
       <c r="I21" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="J21" t="n">
-        <v>0.003927258003375558</v>
+        <v>0.003877679981363975</v>
       </c>
       <c r="K21" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
     </row>
     <row r="22">
@@ -1245,7 +1245,7 @@
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.008064012787509046</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.008064012787509046</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.01414493049880368</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01414493049880368</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.01904648974658279</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01904648974658279</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.02317251719325205</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02317251719325205</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.02674600741059475</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.02674600741059475</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>4.15</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.0155450848915837</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0155450848915837</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         <v>4.15</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.0272673359013083</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0272673359013083</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>4.15</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.03671612481268972</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03671612481268972</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>4.15</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.04466991266169069</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.04466991266169069</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>4.15</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.05155856850235133</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.05155856850235133</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>300</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0002150403410002412</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0002150403410002412</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>300</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0003771981466347649</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0003771981466347649</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>300</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0005079063932422078</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0005079063932422078</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1726,19 +1726,19 @@
         <v>300</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0006179337918200545</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.002812259312039597</v>
       </c>
       <c r="G35" t="n">
         <v>0.00752698044642857</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.00270196970049451</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0006179337918200545</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1763,19 +1763,19 @@
         <v>300</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0007132268642825267</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.002812259312039597</v>
       </c>
       <c r="G36" t="n">
         <v>0.00752698044642857</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.00270196970049451</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0007132268642825267</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1783,296 +1783,6 @@
       <c r="K36" t="n">
         <v>0.0007132268642825267</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1.288702359378202</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.292322196915</v>
-      </c>
-      <c r="G38" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B39" t="n">
-        <v>2.54407371109254</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="F39" t="n">
-        <v>2.545220770381199</v>
-      </c>
-      <c r="G39" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B40" t="n">
-        <v>3.177179490049656</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="F40" t="n">
-        <v>3.177174898781125</v>
-      </c>
-      <c r="G40" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B41" t="n">
-        <v>3.177179490049656</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="F41" t="n">
-        <v>3.177174898781125</v>
-      </c>
-      <c r="G41" t="n">
-        <v>29.17576036758886</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>RE_WT_s_3.3 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E42" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>RE_WT_s_3.3 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E43" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>RE_WT_s_3.3 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>RE_WT_s_3.3 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>RE_WT_s_3.3 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E46" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Hermenches/investment_decision/Hermenches_district_investment_decision.xlsx
+++ b/data/Hermenches/investment_decision/Hermenches_district_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,44 +441,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
@@ -490,7 +491,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
@@ -505,19 +506,19 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>1.002774612488435</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.29226874189296</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.29226874189296</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -527,7 +528,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
@@ -542,19 +543,19 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.488379470582734</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.29226874189296</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.29226874189296</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -564,7 +565,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
@@ -579,19 +580,19 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>1.770880262100316</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.29226874189296</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.29226874189296</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -601,7 +602,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
@@ -616,19 +617,19 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>1.954403657032222</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.29226874189296</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.29226874189296</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -638,7 +639,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
@@ -653,19 +654,19 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>2.082856964215745</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.29226874189296</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.29226874189296</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -675,25 +676,25 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
+        <v>0.08107694156772062</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.08107694156772063</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.002774612488435</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.08107694156772062</v>
       </c>
       <c r="G7" t="n">
         <v>3.29226874189296</v>
@@ -702,7 +703,7 @@
         <v>0.08107694156772063</v>
       </c>
       <c r="I7" t="n">
-        <v>3.29226874189296</v>
+        <v>1.002774612488435</v>
       </c>
       <c r="J7" t="n">
         <v>0.08107694156772061</v>
@@ -712,34 +713,34 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
+        <v>0.08166422014075095</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08166422014075093</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.08176476766181393</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="I8" t="n">
         <v>1.488379470582734</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.08166422014075095</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.29226874189296</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.08166422014075093</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.29226874189296</v>
       </c>
       <c r="J8" t="n">
         <v>0.08176476766181393</v>
@@ -749,34 +750,34 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
+        <v>0.08261203023901018</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.08261203023901016</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.08262513138655603</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="I9" t="n">
         <v>1.770880262100316</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.08261203023901018</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.29226874189296</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.08261203023901016</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.29226874189296</v>
       </c>
       <c r="J9" t="n">
         <v>0.08260826706804172</v>
@@ -786,34 +787,34 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
+        <v>0.08133311667316744</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.08106090679216499</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.08262513138655601</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="I10" t="n">
         <v>1.954403657032222</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.08133311667316744</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.29226874189296</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.08106090679216499</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.29226874189296</v>
       </c>
       <c r="J10" t="n">
         <v>0.08261203023901018</v>
@@ -823,34 +824,34 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
+        <v>0.08102196079476225</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.08076210030521676</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.08193730529246272</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>DH_HP_Water_s_1 MW_d_Hermenches</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="I11" t="n">
         <v>2.082856964215745</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.08102196079476225</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3.29226874189296</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.08076210030521676</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.29226874189296</v>
       </c>
       <c r="J11" t="n">
         <v>0.08192420414491686</v>
@@ -860,7 +861,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
@@ -875,19 +876,19 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.0361830095566004</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -897,7 +898,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
@@ -912,19 +913,19 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.06235215139065679</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -934,7 +935,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
@@ -949,19 +950,19 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.08284414207442109</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -971,7 +972,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
@@ -986,19 +987,19 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.09971239592410397</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1008,7 +1009,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
@@ -1023,19 +1024,19 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.1140828146841643</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1045,7 +1046,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
@@ -1082,11 +1083,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.003443887231061067</v>
+        <v>0.003439290772955338</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,13 +1101,13 @@
         <v>2.331551124703651</v>
       </c>
       <c r="F18" t="n">
-        <v>0.003439290772955338</v>
+        <v>0.003439290772955337</v>
       </c>
       <c r="G18" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="H18" t="n">
-        <v>0.003439290772955337</v>
+        <v>0.003443887231061067</v>
       </c>
       <c r="I18" t="n">
         <v>2.331551124703651</v>
@@ -1119,11 +1120,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.003510231617690212</v>
+        <v>0.003497220638844078</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,13 +1138,13 @@
         <v>2.331551124703651</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003497220638844078</v>
+        <v>0.003497220638844079</v>
       </c>
       <c r="G19" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="H19" t="n">
-        <v>0.003497220638844079</v>
+        <v>0.003510231617690212</v>
       </c>
       <c r="I19" t="n">
         <v>2.331551124703651</v>
@@ -1156,11 +1157,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.003941639315975926</v>
+        <v>0.003904701122929663</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,13 +1175,13 @@
         <v>2.331551124703651</v>
       </c>
       <c r="F20" t="n">
-        <v>0.003904701122929663</v>
+        <v>0.00391714500320406</v>
       </c>
       <c r="G20" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00391714500320406</v>
+        <v>0.003941639315975926</v>
       </c>
       <c r="I20" t="n">
         <v>2.331551124703651</v>
@@ -1193,11 +1194,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.003973082794563049</v>
+        <v>0.003918925391656758</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,13 +1212,13 @@
         <v>2.331551124703651</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003918925391656758</v>
+        <v>0.003930804728321693</v>
       </c>
       <c r="G21" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="H21" t="n">
-        <v>0.003930804728321693</v>
+        <v>0.003973082794563049</v>
       </c>
       <c r="I21" t="n">
         <v>2.331551124703651</v>
@@ -1230,7 +1231,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1245,7 +1246,7 @@
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.008064012787509046</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1257,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.008064012787509046</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1282,7 +1283,7 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01414493049880368</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1294,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.01414493049880368</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1304,7 +1305,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1319,7 +1320,7 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01904648974658279</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1331,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.01904648974658279</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1356,7 +1357,7 @@
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02317251719325205</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1368,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.02317251719325205</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1378,7 +1379,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1393,7 +1394,7 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02674600741059475</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1405,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.02674600741059475</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1415,7 +1416,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1430,7 +1431,7 @@
         <v>4.15</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0155450848915837</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1442,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.0155450848915837</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1452,7 +1453,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1467,7 +1468,7 @@
         <v>4.15</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0272673359013083</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1479,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.0272673359013083</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1489,7 +1490,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
@@ -1504,7 +1505,7 @@
         <v>4.15</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03671612481268972</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1516,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.03671612481268972</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1526,7 +1527,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
@@ -1541,7 +1542,7 @@
         <v>4.15</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04466991266169069</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1553,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.04466991266169069</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1563,7 +1564,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
@@ -1578,7 +1579,7 @@
         <v>4.15</v>
       </c>
       <c r="E31" t="n">
-        <v>0.05155856850235133</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1590,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.05155856850235133</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1600,7 +1601,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1615,29 +1616,29 @@
         <v>300</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0002150403410002412</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.002150403410002412</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0002150403410002412</v>
+        <v>0.002150403410002412</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1652,29 +1653,29 @@
         <v>300</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003771981466347649</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.003771981466347649</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003771981466347649</v>
+        <v>0.003771981466347649</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1689,33 +1690,33 @@
         <v>300</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0005079063932422078</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.005079063932422078</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0005079063932422078</v>
+        <v>0.005079063932422078</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>0.02812259312039597</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1726,33 +1727,33 @@
         <v>300</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0006179337918200545</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="F35" t="n">
-        <v>0.002812259312039597</v>
+        <v>0.0270196970049451</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00270196970049451</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.006179337918200545</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0006179337918200545</v>
+        <v>0.006179337918200545</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>0.02812259312039597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1763,25 +1764,25 @@
         <v>300</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0007132268642825267</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="F36" t="n">
-        <v>0.002812259312039597</v>
+        <v>0.0270196970049451</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00270196970049451</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.007132268642825267</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0007132268642825267</v>
+        <v>0.007132268642825267</v>
       </c>
     </row>
   </sheetData>
